--- a/artfynd/A 8817-2025 artfynd.xlsx
+++ b/artfynd/A 8817-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>6777616</v>
       </c>
       <c r="B2" t="n">
-        <v>101679</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688374.2323707298</v>
+        <v>688374</v>
       </c>
       <c r="R2" t="n">
-        <v>6608207.519264563</v>
+        <v>6608208</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2005-09-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-09-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
